--- a/data/valuations/ASTS/ASTS_modelo_valoracion.xlsx
+++ b/data/valuations/ASTS/ASTS_modelo_valoracion.xlsx
@@ -627,19 +627,19 @@
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.13</v>
+        <v>7.1858</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.11</v>
+        <v>6.4672</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.09</v>
+        <v>5.7486</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.06999999999999999</v>
+        <v>5.0301</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.04999999999999999</v>
+        <v>4.3115</v>
       </c>
     </row>
     <row r="9">
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>-0.1075</v>
+        <v>7.1858</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.08749999999999999</v>
+        <v>6.4672</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.0675</v>
+        <v>5.7486</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.0475</v>
+        <v>5.0301</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>-0.0275</v>
+        <v>4.3115</v>
       </c>
     </row>
     <row r="10">
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-0.1525</v>
+        <v>7.1858</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.1325</v>
+        <v>6.4672</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.1125</v>
+        <v>5.7486</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.09249999999999999</v>
+        <v>5.0301</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.07249999999999998</v>
+        <v>4.3115</v>
       </c>
     </row>
     <row r="11">
@@ -785,19 +785,19 @@
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.6825948465283858</v>
+        <v>0.6725948465283857</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.6825948465283858</v>
+        <v>0.6725948465283857</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.6825948465283858</v>
+        <v>0.6725948465283857</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.6825948465283858</v>
+        <v>0.6725948465283857</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.6825948465283858</v>
+        <v>0.6725948465283857</v>
       </c>
     </row>
     <row r="17">
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.6625948465283857</v>
+        <v>0.6725948465283857</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.6625948465283857</v>
+        <v>0.6725948465283857</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.6625948465283857</v>
+        <v>0.6725948465283857</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.6625948465283857</v>
+        <v>0.6725948465283857</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.6625948465283857</v>
+        <v>0.6725948465283857</v>
       </c>
     </row>
     <row r="18">
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.01</v>
+        <v>6.288334945389496</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.01</v>
+        <v>6.288334945389496</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.01</v>
+        <v>6.288334945389496</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.01</v>
+        <v>6.288334945389496</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.01</v>
+        <v>6.288334945389496</v>
       </c>
     </row>
     <row r="21">
@@ -878,19 +878,19 @@
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.01</v>
+        <v>6.288334945389496</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.01</v>
+        <v>6.288334945389496</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.01</v>
+        <v>6.288334945389496</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.01</v>
+        <v>6.288334945389496</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.01</v>
+        <v>6.288334945389496</v>
       </c>
     </row>
     <row r="22">
@@ -900,19 +900,19 @@
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.01</v>
+        <v>6.288334945389496</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.01</v>
+        <v>6.288334945389496</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.01</v>
+        <v>6.288334945389496</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.01</v>
+        <v>6.288334945389496</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.01</v>
+        <v>6.288334945389496</v>
       </c>
     </row>
     <row r="23">
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.1916</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="36">
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.1816</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="37">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.2016</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="38">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>76.08499999999999</v>
+        <v>68.93000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="C32" s="18" t="n">
-        <v>292.637039</v>
+        <v>298.678735</v>
       </c>
     </row>
     <row r="33">
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/76.085-1</f>
+        <f>C33/68.93-1</f>
         <v/>
       </c>
     </row>
@@ -3501,202 +3501,202 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>17x</t>
+          <t>8x</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>19x</t>
+          <t>10x</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>21x</t>
+          <t>12x</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>23x</t>
+          <t>14x</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>16x</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.1616</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C39" s="22">
-        <f>(F$12/(1+$A$39)^1+G$12/(1+$A$39)^2+H$12/(1+$A$39)^3+I$12/(1+$A$39)^4+J$12/(1+$A$39)^5+J$8*17/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$39)^1+G$12/(1+$A$39)^2+H$12/(1+$A$39)^3+I$12/(1+$A$39)^4+J$12/(1+$A$39)^5+J$8*8/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(F$12/(1+$A$39)^1+G$12/(1+$A$39)^2+H$12/(1+$A$39)^3+I$12/(1+$A$39)^4+J$12/(1+$A$39)^5+J$8*19/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$39)^1+G$12/(1+$A$39)^2+H$12/(1+$A$39)^3+I$12/(1+$A$39)^4+J$12/(1+$A$39)^5+J$8*10/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(F$12/(1+$A$39)^1+G$12/(1+$A$39)^2+H$12/(1+$A$39)^3+I$12/(1+$A$39)^4+J$12/(1+$A$39)^5+J$8*21/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$39)^1+G$12/(1+$A$39)^2+H$12/(1+$A$39)^3+I$12/(1+$A$39)^4+J$12/(1+$A$39)^5+J$8*12/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(F$12/(1+$A$39)^1+G$12/(1+$A$39)^2+H$12/(1+$A$39)^3+I$12/(1+$A$39)^4+J$12/(1+$A$39)^5+J$8*23/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$39)^1+G$12/(1+$A$39)^2+H$12/(1+$A$39)^3+I$12/(1+$A$39)^4+J$12/(1+$A$39)^5+J$8*14/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(F$12/(1+$A$39)^1+G$12/(1+$A$39)^2+H$12/(1+$A$39)^3+I$12/(1+$A$39)^4+J$12/(1+$A$39)^5+J$8*25/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$39)^1+G$12/(1+$A$39)^2+H$12/(1+$A$39)^3+I$12/(1+$A$39)^4+J$12/(1+$A$39)^5+J$8*16/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.1716</v>
+        <v>0.08</v>
       </c>
       <c r="C40" s="22">
-        <f>(F$12/(1+$A$40)^1+G$12/(1+$A$40)^2+H$12/(1+$A$40)^3+I$12/(1+$A$40)^4+J$12/(1+$A$40)^5+J$8*17/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$40)^1+G$12/(1+$A$40)^2+H$12/(1+$A$40)^3+I$12/(1+$A$40)^4+J$12/(1+$A$40)^5+J$8*8/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(F$12/(1+$A$40)^1+G$12/(1+$A$40)^2+H$12/(1+$A$40)^3+I$12/(1+$A$40)^4+J$12/(1+$A$40)^5+J$8*19/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$40)^1+G$12/(1+$A$40)^2+H$12/(1+$A$40)^3+I$12/(1+$A$40)^4+J$12/(1+$A$40)^5+J$8*10/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(F$12/(1+$A$40)^1+G$12/(1+$A$40)^2+H$12/(1+$A$40)^3+I$12/(1+$A$40)^4+J$12/(1+$A$40)^5+J$8*21/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$40)^1+G$12/(1+$A$40)^2+H$12/(1+$A$40)^3+I$12/(1+$A$40)^4+J$12/(1+$A$40)^5+J$8*12/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(F$12/(1+$A$40)^1+G$12/(1+$A$40)^2+H$12/(1+$A$40)^3+I$12/(1+$A$40)^4+J$12/(1+$A$40)^5+J$8*23/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$40)^1+G$12/(1+$A$40)^2+H$12/(1+$A$40)^3+I$12/(1+$A$40)^4+J$12/(1+$A$40)^5+J$8*14/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(F$12/(1+$A$40)^1+G$12/(1+$A$40)^2+H$12/(1+$A$40)^3+I$12/(1+$A$40)^4+J$12/(1+$A$40)^5+J$8*25/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$40)^1+G$12/(1+$A$40)^2+H$12/(1+$A$40)^3+I$12/(1+$A$40)^4+J$12/(1+$A$40)^5+J$8*16/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.1816</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="C41" s="22">
-        <f>(F$12/(1+$A$41)^1+G$12/(1+$A$41)^2+H$12/(1+$A$41)^3+I$12/(1+$A$41)^4+J$12/(1+$A$41)^5+J$8*17/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$41)^1+G$12/(1+$A$41)^2+H$12/(1+$A$41)^3+I$12/(1+$A$41)^4+J$12/(1+$A$41)^5+J$8*8/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(F$12/(1+$A$41)^1+G$12/(1+$A$41)^2+H$12/(1+$A$41)^3+I$12/(1+$A$41)^4+J$12/(1+$A$41)^5+J$8*19/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$41)^1+G$12/(1+$A$41)^2+H$12/(1+$A$41)^3+I$12/(1+$A$41)^4+J$12/(1+$A$41)^5+J$8*10/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(F$12/(1+$A$41)^1+G$12/(1+$A$41)^2+H$12/(1+$A$41)^3+I$12/(1+$A$41)^4+J$12/(1+$A$41)^5+J$8*21/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$41)^1+G$12/(1+$A$41)^2+H$12/(1+$A$41)^3+I$12/(1+$A$41)^4+J$12/(1+$A$41)^5+J$8*12/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(F$12/(1+$A$41)^1+G$12/(1+$A$41)^2+H$12/(1+$A$41)^3+I$12/(1+$A$41)^4+J$12/(1+$A$41)^5+J$8*23/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$41)^1+G$12/(1+$A$41)^2+H$12/(1+$A$41)^3+I$12/(1+$A$41)^4+J$12/(1+$A$41)^5+J$8*14/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(F$12/(1+$A$41)^1+G$12/(1+$A$41)^2+H$12/(1+$A$41)^3+I$12/(1+$A$41)^4+J$12/(1+$A$41)^5+J$8*25/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$41)^1+G$12/(1+$A$41)^2+H$12/(1+$A$41)^3+I$12/(1+$A$41)^4+J$12/(1+$A$41)^5+J$8*16/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.1916</v>
+        <v>0.1</v>
       </c>
       <c r="C42" s="22">
-        <f>(F$12/(1+$A$42)^1+G$12/(1+$A$42)^2+H$12/(1+$A$42)^3+I$12/(1+$A$42)^4+J$12/(1+$A$42)^5+J$8*17/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$42)^1+G$12/(1+$A$42)^2+H$12/(1+$A$42)^3+I$12/(1+$A$42)^4+J$12/(1+$A$42)^5+J$8*8/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(F$12/(1+$A$42)^1+G$12/(1+$A$42)^2+H$12/(1+$A$42)^3+I$12/(1+$A$42)^4+J$12/(1+$A$42)^5+J$8*19/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$42)^1+G$12/(1+$A$42)^2+H$12/(1+$A$42)^3+I$12/(1+$A$42)^4+J$12/(1+$A$42)^5+J$8*10/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(F$12/(1+$A$42)^1+G$12/(1+$A$42)^2+H$12/(1+$A$42)^3+I$12/(1+$A$42)^4+J$12/(1+$A$42)^5+J$8*21/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$42)^1+G$12/(1+$A$42)^2+H$12/(1+$A$42)^3+I$12/(1+$A$42)^4+J$12/(1+$A$42)^5+J$8*12/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(F$12/(1+$A$42)^1+G$12/(1+$A$42)^2+H$12/(1+$A$42)^3+I$12/(1+$A$42)^4+J$12/(1+$A$42)^5+J$8*23/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$42)^1+G$12/(1+$A$42)^2+H$12/(1+$A$42)^3+I$12/(1+$A$42)^4+J$12/(1+$A$42)^5+J$8*14/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(F$12/(1+$A$42)^1+G$12/(1+$A$42)^2+H$12/(1+$A$42)^3+I$12/(1+$A$42)^4+J$12/(1+$A$42)^5+J$8*25/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$42)^1+G$12/(1+$A$42)^2+H$12/(1+$A$42)^3+I$12/(1+$A$42)^4+J$12/(1+$A$42)^5+J$8*16/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.2016</v>
+        <v>0.11</v>
       </c>
       <c r="C43" s="22">
-        <f>(F$12/(1+$A$43)^1+G$12/(1+$A$43)^2+H$12/(1+$A$43)^3+I$12/(1+$A$43)^4+J$12/(1+$A$43)^5+J$8*17/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$43)^1+G$12/(1+$A$43)^2+H$12/(1+$A$43)^3+I$12/(1+$A$43)^4+J$12/(1+$A$43)^5+J$8*8/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(F$12/(1+$A$43)^1+G$12/(1+$A$43)^2+H$12/(1+$A$43)^3+I$12/(1+$A$43)^4+J$12/(1+$A$43)^5+J$8*19/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$43)^1+G$12/(1+$A$43)^2+H$12/(1+$A$43)^3+I$12/(1+$A$43)^4+J$12/(1+$A$43)^5+J$8*10/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(F$12/(1+$A$43)^1+G$12/(1+$A$43)^2+H$12/(1+$A$43)^3+I$12/(1+$A$43)^4+J$12/(1+$A$43)^5+J$8*21/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$43)^1+G$12/(1+$A$43)^2+H$12/(1+$A$43)^3+I$12/(1+$A$43)^4+J$12/(1+$A$43)^5+J$8*12/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(F$12/(1+$A$43)^1+G$12/(1+$A$43)^2+H$12/(1+$A$43)^3+I$12/(1+$A$43)^4+J$12/(1+$A$43)^5+J$8*23/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$43)^1+G$12/(1+$A$43)^2+H$12/(1+$A$43)^3+I$12/(1+$A$43)^4+J$12/(1+$A$43)^5+J$8*14/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(F$12/(1+$A$43)^1+G$12/(1+$A$43)^2+H$12/(1+$A$43)^3+I$12/(1+$A$43)^4+J$12/(1+$A$43)^5+J$8*25/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$43)^1+G$12/(1+$A$43)^2+H$12/(1+$A$43)^3+I$12/(1+$A$43)^4+J$12/(1+$A$43)^5+J$8*16/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.2116</v>
+        <v>0.12</v>
       </c>
       <c r="C44" s="22">
-        <f>(F$12/(1+$A$44)^1+G$12/(1+$A$44)^2+H$12/(1+$A$44)^3+I$12/(1+$A$44)^4+J$12/(1+$A$44)^5+J$8*17/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$44)^1+G$12/(1+$A$44)^2+H$12/(1+$A$44)^3+I$12/(1+$A$44)^4+J$12/(1+$A$44)^5+J$8*8/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(F$12/(1+$A$44)^1+G$12/(1+$A$44)^2+H$12/(1+$A$44)^3+I$12/(1+$A$44)^4+J$12/(1+$A$44)^5+J$8*19/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$44)^1+G$12/(1+$A$44)^2+H$12/(1+$A$44)^3+I$12/(1+$A$44)^4+J$12/(1+$A$44)^5+J$8*10/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(F$12/(1+$A$44)^1+G$12/(1+$A$44)^2+H$12/(1+$A$44)^3+I$12/(1+$A$44)^4+J$12/(1+$A$44)^5+J$8*21/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$44)^1+G$12/(1+$A$44)^2+H$12/(1+$A$44)^3+I$12/(1+$A$44)^4+J$12/(1+$A$44)^5+J$8*12/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(F$12/(1+$A$44)^1+G$12/(1+$A$44)^2+H$12/(1+$A$44)^3+I$12/(1+$A$44)^4+J$12/(1+$A$44)^5+J$8*23/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$44)^1+G$12/(1+$A$44)^2+H$12/(1+$A$44)^3+I$12/(1+$A$44)^4+J$12/(1+$A$44)^5+J$8*14/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(F$12/(1+$A$44)^1+G$12/(1+$A$44)^2+H$12/(1+$A$44)^3+I$12/(1+$A$44)^4+J$12/(1+$A$44)^5+J$8*25/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$44)^1+G$12/(1+$A$44)^2+H$12/(1+$A$44)^3+I$12/(1+$A$44)^4+J$12/(1+$A$44)^5+J$8*16/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.2216</v>
+        <v>0.13</v>
       </c>
       <c r="C45" s="22">
-        <f>(F$12/(1+$A$45)^1+G$12/(1+$A$45)^2+H$12/(1+$A$45)^3+I$12/(1+$A$45)^4+J$12/(1+$A$45)^5+J$8*17/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$45)^1+G$12/(1+$A$45)^2+H$12/(1+$A$45)^3+I$12/(1+$A$45)^4+J$12/(1+$A$45)^5+J$8*8/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(F$12/(1+$A$45)^1+G$12/(1+$A$45)^2+H$12/(1+$A$45)^3+I$12/(1+$A$45)^4+J$12/(1+$A$45)^5+J$8*19/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$45)^1+G$12/(1+$A$45)^2+H$12/(1+$A$45)^3+I$12/(1+$A$45)^4+J$12/(1+$A$45)^5+J$8*10/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(F$12/(1+$A$45)^1+G$12/(1+$A$45)^2+H$12/(1+$A$45)^3+I$12/(1+$A$45)^4+J$12/(1+$A$45)^5+J$8*21/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$45)^1+G$12/(1+$A$45)^2+H$12/(1+$A$45)^3+I$12/(1+$A$45)^4+J$12/(1+$A$45)^5+J$8*12/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(F$12/(1+$A$45)^1+G$12/(1+$A$45)^2+H$12/(1+$A$45)^3+I$12/(1+$A$45)^4+J$12/(1+$A$45)^5+J$8*23/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$45)^1+G$12/(1+$A$45)^2+H$12/(1+$A$45)^3+I$12/(1+$A$45)^4+J$12/(1+$A$45)^5+J$8*14/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(F$12/(1+$A$45)^1+G$12/(1+$A$45)^2+H$12/(1+$A$45)^3+I$12/(1+$A$45)^4+J$12/(1+$A$45)^5+J$8*25/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(F$12/(1+$A$45)^1+G$12/(1+$A$45)^2+H$12/(1+$A$45)^3+I$12/(1+$A$45)^4+J$12/(1+$A$45)^5+J$8*16/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
